--- a/converted/tozalangan/baliqchi/Sentabr 10 kunlik/Elektr Qoidabuzarliklar.xlsx
+++ b/converted/tozalangan/baliqchi/Sentabr 10 kunlik/Elektr Qoidabuzarliklar.xlsx
@@ -11,9 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="81">
   <si>
     <t>Qoidabuzarliklar Sentabr (1–10) Holatiga Ko'ra</t>
+  </si>
+  <si>
+    <t>Podstansiya</t>
+  </si>
+  <si>
+    <t>Fider</t>
   </si>
   <si>
     <t>TP Nomi</t>
@@ -666,18 +672,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="7" width="18" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="12" width="26" customWidth="1"/>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="9" width="18" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -692,8 +698,10 @@
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1"/>
+      <c r="N1"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -718,10 +726,10 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="5" t="s">
@@ -730,63 +738,63 @@
       <c r="L2" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="M2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="N2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1">
+    </row>
+    <row r="3" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1">
         <v>46268</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2">
         <v>280800</v>
       </c>
-      <c r="G3" s="2">
+      <c r="I3" s="2">
         <v>432</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
       </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
       <c r="L3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="N3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1">
         <v>46267</v>
       </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2">
         <v>174850</v>
       </c>
-      <c r="G4" s="2">
+      <c r="I4" s="2">
         <v>269</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
       </c>
       <c r="J4" t="s">
         <v>24</v>
@@ -797,418 +805,424 @@
       <c r="L4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="M4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1">
         <v>46274</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
       </c>
       <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46275</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46275</v>
+      </c>
+      <c r="G9" t="s">
         <v>30</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46274</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46274</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1">
         <v>46267</v>
       </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="G10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="2">
         <v>187200</v>
       </c>
-      <c r="G10" s="2">
+      <c r="I10" s="2">
         <v>288</v>
       </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>52</v>
-      </c>
       <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G11" t="s">
         <v>53</v>
       </c>
-      <c r="K10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="H11" s="2">
+        <v>187200</v>
+      </c>
+      <c r="I11" s="2">
+        <v>288</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="M11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1">
         <v>46267</v>
       </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="2">
-        <v>187200</v>
-      </c>
-      <c r="G11" s="2">
-        <v>288</v>
-      </c>
-      <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46267</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="2">
         <v>421200</v>
       </c>
-      <c r="G12" s="2">
+      <c r="I12" s="2">
         <v>648</v>
       </c>
-      <c r="H12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" t="s">
-        <v>60</v>
-      </c>
       <c r="J12" t="s">
-        <v>61</v>
+        <v>18</v>
+      </c>
+      <c r="K12" t="s">
+        <v>62</v>
       </c>
       <c r="L12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
         <v>63</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="N12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1">
         <v>46268</v>
       </c>
-      <c r="E13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="2">
         <v>514800</v>
       </c>
-      <c r="G13" s="2">
+      <c r="I13" s="2">
         <v>792</v>
       </c>
-      <c r="H13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" t="s">
-        <v>65</v>
-      </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>18</v>
+      </c>
+      <c r="K13" t="s">
+        <v>67</v>
       </c>
       <c r="L13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="N13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="1">
         <v>46270</v>
       </c>
-      <c r="E14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" t="s">
-        <v>70</v>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="L14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
         <v>73</v>
       </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="M14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1">
         <v>46272</v>
       </c>
-      <c r="E15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" t="s">
-        <v>74</v>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
       </c>
       <c r="J15" t="s">
         <v>24</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="L15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="1">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1">
         <v>46272</v>
       </c>
-      <c r="E16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
-        <v>77</v>
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="K16" t="s">
+        <v>79</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>47</v>
+      </c>
+      <c r="N16" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
